--- a/BWI/bestwine_output/bestwine_Israel.xlsx
+++ b/BWI/bestwine_output/bestwine_Israel.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA127"/>
+  <dimension ref="A1:AA128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -13375,6 +13375,103 @@
         </is>
       </c>
     </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Wine &amp; More</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>Wine &amp; More</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>22490</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>Tel Aviv-Yafo</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>Tel Aviv District</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>8 Nahum Goldmann Street</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>3460884</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>https://wineandmore.konimbo.co.il, https://www.wineandmore.co.il</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr"/>
+      <c r="K128" s="2" t="inlineStr"/>
+      <c r="L128" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="M128" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N128" s="2" t="inlineStr">
+        <is>
+          <t>marketing@wineandmore.co.il</t>
+        </is>
+      </c>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>+972 74-704-3304</t>
+        </is>
+      </c>
+      <c r="P128" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="Q128" s="2" t="inlineStr">
+        <is>
+          <t>513510867</t>
+        </is>
+      </c>
+      <c r="R128" s="2" t="inlineStr"/>
+      <c r="S128" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/WineandMor</t>
+        </is>
+      </c>
+      <c r="T128" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/wineandmore.il/</t>
+        </is>
+      </c>
+      <c r="U128" s="2" t="inlineStr"/>
+      <c r="V128" s="2" t="inlineStr"/>
+      <c r="W128" s="2" t="inlineStr"/>
+      <c r="X128" s="2" t="inlineStr"/>
+      <c r="Y128" s="2" t="inlineStr"/>
+      <c r="Z128" s="2" t="inlineStr"/>
+      <c r="AA128" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Israel.xlsx
+++ b/BWI/bestwine_output/bestwine_Israel.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA128"/>
+  <dimension ref="A1:AA129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -13472,6 +13472,103 @@
       <c r="Z128" s="2" t="inlineStr"/>
       <c r="AA128" s="2" t="inlineStr"/>
     </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>Wine &amp; More</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>Wine &amp; More</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>22490</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>Tel Aviv-Yafo</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>Tel Aviv District</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>8 Nahum Goldmann Street</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>3460884</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>https://wineandmore.konimbo.co.il, https://www.wineandmore.co.il</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr"/>
+      <c r="K129" s="2" t="inlineStr"/>
+      <c r="L129" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="M129" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N129" s="2" t="inlineStr">
+        <is>
+          <t>marketing@wineandmore.co.il</t>
+        </is>
+      </c>
+      <c r="O129" s="2" t="inlineStr">
+        <is>
+          <t>+972 74-704-3304</t>
+        </is>
+      </c>
+      <c r="P129" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="Q129" s="2" t="inlineStr">
+        <is>
+          <t>513510867</t>
+        </is>
+      </c>
+      <c r="R129" s="2" t="inlineStr"/>
+      <c r="S129" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/WineandMor</t>
+        </is>
+      </c>
+      <c r="T129" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/wineandmore.il/</t>
+        </is>
+      </c>
+      <c r="U129" s="2" t="inlineStr"/>
+      <c r="V129" s="2" t="inlineStr"/>
+      <c r="W129" s="2" t="inlineStr"/>
+      <c r="X129" s="2" t="inlineStr"/>
+      <c r="Y129" s="2" t="inlineStr"/>
+      <c r="Z129" s="2" t="inlineStr"/>
+      <c r="AA129" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Israel.xlsx
+++ b/BWI/bestwine_output/bestwine_Israel.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA129"/>
+  <dimension ref="A1:AA130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -13569,6 +13569,103 @@
       <c r="Z129" s="2" t="inlineStr"/>
       <c r="AA129" s="2" t="inlineStr"/>
     </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>Wine &amp; More</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>Wine &amp; More</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>22490</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>Tel Aviv-Yafo</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>Tel Aviv District</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>8 Nahum Goldmann Street</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>3460884</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>https://wineandmore.konimbo.co.il, https://www.wineandmore.co.il</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr"/>
+      <c r="K130" s="2" t="inlineStr"/>
+      <c r="L130" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="M130" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N130" s="2" t="inlineStr">
+        <is>
+          <t>marketing@wineandmore.co.il</t>
+        </is>
+      </c>
+      <c r="O130" s="2" t="inlineStr">
+        <is>
+          <t>+972 74-704-3304</t>
+        </is>
+      </c>
+      <c r="P130" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="Q130" s="2" t="inlineStr">
+        <is>
+          <t>513510867</t>
+        </is>
+      </c>
+      <c r="R130" s="2" t="inlineStr"/>
+      <c r="S130" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/WineandMor</t>
+        </is>
+      </c>
+      <c r="T130" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/wineandmore.il/</t>
+        </is>
+      </c>
+      <c r="U130" s="2" t="inlineStr"/>
+      <c r="V130" s="2" t="inlineStr"/>
+      <c r="W130" s="2" t="inlineStr"/>
+      <c r="X130" s="2" t="inlineStr"/>
+      <c r="Y130" s="2" t="inlineStr"/>
+      <c r="Z130" s="2" t="inlineStr"/>
+      <c r="AA130" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
